--- a/03_Learning_Management/00_Excel_Export/priorities.xlsx
+++ b/03_Learning_Management/00_Excel_Export/priorities.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,72 +415,72 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B2" t="str">
-        <v>Talks</v>
+        <v>Communication Skill</v>
       </c>
       <c r="C2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="D2">
-        <v>201</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B3" t="str">
-        <v>HTML</v>
+        <v>English</v>
       </c>
       <c r="C3">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="D3">
-        <v>202</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B4" t="str">
-        <v>CSS</v>
+        <v>Aptitude</v>
       </c>
       <c r="C4">
-        <v>203</v>
+        <v>103</v>
       </c>
       <c r="D4">
-        <v>203</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B5" t="str">
-        <v>JavaScript</v>
+        <v>General Learning</v>
       </c>
       <c r="C5">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="D5">
-        <v>204</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B6" t="str">
-        <v>FrontEnd</v>
+        <v>Maths</v>
       </c>
       <c r="C6">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="D6">
-        <v>205</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -488,13 +488,13 @@
         <v>WebDev</v>
       </c>
       <c r="B7" t="str">
-        <v>Git</v>
+        <v>Talks</v>
       </c>
       <c r="C7">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D7">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
@@ -502,13 +502,13 @@
         <v>WebDev</v>
       </c>
       <c r="B8" t="str">
-        <v>NodeJS</v>
+        <v>HTML</v>
       </c>
       <c r="C8">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D8">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -516,13 +516,13 @@
         <v>WebDev</v>
       </c>
       <c r="B9" t="str">
-        <v>ExpressJS</v>
+        <v>CSS</v>
       </c>
       <c r="C9">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D9">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -530,13 +530,13 @@
         <v>WebDev</v>
       </c>
       <c r="B10" t="str">
-        <v>ReactJS</v>
+        <v>JavaScript</v>
       </c>
       <c r="C10">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D10">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -544,13 +544,13 @@
         <v>WebDev</v>
       </c>
       <c r="B11" t="str">
-        <v>Redux</v>
+        <v>FrontEnd</v>
       </c>
       <c r="C11">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D11">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -558,13 +558,13 @@
         <v>WebDev</v>
       </c>
       <c r="B12" t="str">
-        <v>MongoDB</v>
+        <v>Git</v>
       </c>
       <c r="C12">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D12">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -572,13 +572,13 @@
         <v>WebDev</v>
       </c>
       <c r="B13" t="str">
-        <v>SQL</v>
+        <v>NodeJS</v>
       </c>
       <c r="C13">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D13">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
@@ -586,13 +586,13 @@
         <v>WebDev</v>
       </c>
       <c r="B14" t="str">
-        <v>MySQL</v>
+        <v>ExpressJS</v>
       </c>
       <c r="C14">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D14">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -600,13 +600,13 @@
         <v>WebDev</v>
       </c>
       <c r="B15" t="str">
-        <v>Backend</v>
+        <v>ReactJS</v>
       </c>
       <c r="C15">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D15">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16">
@@ -614,13 +614,13 @@
         <v>WebDev</v>
       </c>
       <c r="B16" t="str">
-        <v>BootStrap</v>
+        <v>Redux</v>
       </c>
       <c r="C16">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D16">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
@@ -628,13 +628,13 @@
         <v>WebDev</v>
       </c>
       <c r="B17" t="str">
-        <v>Tailwind</v>
+        <v>MongoDB</v>
       </c>
       <c r="C17">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D17">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
@@ -642,13 +642,13 @@
         <v>WebDev</v>
       </c>
       <c r="B18" t="str">
-        <v>MERN</v>
+        <v>SQL</v>
       </c>
       <c r="C18">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D18">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19">
@@ -656,13 +656,13 @@
         <v>WebDev</v>
       </c>
       <c r="B19" t="str">
-        <v>TypeScript</v>
+        <v>MySQL</v>
       </c>
       <c r="C19">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D19">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20">
@@ -670,13 +670,13 @@
         <v>WebDev</v>
       </c>
       <c r="B20" t="str">
-        <v>PostgreSQL</v>
+        <v>Backend</v>
       </c>
       <c r="C20">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D20">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
@@ -684,13 +684,13 @@
         <v>WebDev</v>
       </c>
       <c r="B21" t="str">
-        <v>NextJS</v>
+        <v>BootStrap</v>
       </c>
       <c r="C21">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D21">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -698,13 +698,13 @@
         <v>WebDev</v>
       </c>
       <c r="B22" t="str">
-        <v>DSA</v>
+        <v>Tailwind</v>
       </c>
       <c r="C22">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D22">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23">
@@ -712,13 +712,13 @@
         <v>WebDev</v>
       </c>
       <c r="B23" t="str">
-        <v>Redis</v>
+        <v>MERN</v>
       </c>
       <c r="C23">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D23">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
@@ -726,13 +726,13 @@
         <v>WebDev</v>
       </c>
       <c r="B24" t="str">
-        <v>Supabase</v>
+        <v>TypeScript</v>
       </c>
       <c r="C24">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D24">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25">
@@ -740,13 +740,13 @@
         <v>WebDev</v>
       </c>
       <c r="B25" t="str">
-        <v>NestJS</v>
+        <v>PostgreSQL</v>
       </c>
       <c r="C25">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D25">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26">
@@ -754,13 +754,13 @@
         <v>WebDev</v>
       </c>
       <c r="B26" t="str">
-        <v>Web Dev</v>
+        <v>NextJS</v>
       </c>
       <c r="C26">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D26">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27">
@@ -768,13 +768,13 @@
         <v>WebDev</v>
       </c>
       <c r="B27" t="str">
-        <v>GraphQL</v>
+        <v>DSA</v>
       </c>
       <c r="C27">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D27">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28">
@@ -782,13 +782,13 @@
         <v>WebDev</v>
       </c>
       <c r="B28" t="str">
-        <v>gRPC</v>
+        <v>Redis</v>
       </c>
       <c r="C28">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D28">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
@@ -796,13 +796,13 @@
         <v>WebDev</v>
       </c>
       <c r="B29" t="str">
-        <v>MicroServices</v>
+        <v>Supabase</v>
       </c>
       <c r="C29">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D29">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
@@ -810,18 +810,942 @@
         <v>WebDev</v>
       </c>
       <c r="B30" t="str">
+        <v>NestJS</v>
+      </c>
+      <c r="C30">
+        <v>224</v>
+      </c>
+      <c r="D30">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>WebDev</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Web Dev</v>
+      </c>
+      <c r="C31">
+        <v>225</v>
+      </c>
+      <c r="D31">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>WebDev</v>
+      </c>
+      <c r="B32" t="str">
+        <v>GraphQL</v>
+      </c>
+      <c r="C32">
+        <v>226</v>
+      </c>
+      <c r="D32">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>WebDev</v>
+      </c>
+      <c r="B33" t="str">
+        <v>gRPC</v>
+      </c>
+      <c r="C33">
+        <v>227</v>
+      </c>
+      <c r="D33">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>WebDev</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MicroServices</v>
+      </c>
+      <c r="C34">
+        <v>228</v>
+      </c>
+      <c r="D34">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>WebDev</v>
+      </c>
+      <c r="B35" t="str">
         <v>Concepts</v>
       </c>
-      <c r="C30">
+      <c r="C35">
         <v>229</v>
       </c>
-      <c r="D30">
+      <c r="D35">
         <v>229</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Talks</v>
+      </c>
+      <c r="C36">
+        <v>301</v>
+      </c>
+      <c r="D36">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Docker</v>
+      </c>
+      <c r="C37">
+        <v>302</v>
+      </c>
+      <c r="D37">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SSH</v>
+      </c>
+      <c r="C38">
+        <v>303</v>
+      </c>
+      <c r="D38">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Jenkins</v>
+      </c>
+      <c r="C39">
+        <v>304</v>
+      </c>
+      <c r="D39">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Linux</v>
+      </c>
+      <c r="C40">
+        <v>305</v>
+      </c>
+      <c r="D40">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="C41">
+        <v>306</v>
+      </c>
+      <c r="D41">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B42" t="str">
+        <v>DevOps</v>
+      </c>
+      <c r="C42">
+        <v>307</v>
+      </c>
+      <c r="D42">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B43" t="str">
+        <v>AWS</v>
+      </c>
+      <c r="C43">
+        <v>308</v>
+      </c>
+      <c r="D43">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B44" t="str">
+        <v>ArgoCD</v>
+      </c>
+      <c r="C44">
+        <v>309</v>
+      </c>
+      <c r="D44">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B45" t="str">
+        <v>CloudFlare</v>
+      </c>
+      <c r="C45">
+        <v>310</v>
+      </c>
+      <c r="D45">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Kafka</v>
+      </c>
+      <c r="C46">
+        <v>311</v>
+      </c>
+      <c r="D46">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Concepts</v>
+      </c>
+      <c r="C47">
+        <v>312</v>
+      </c>
+      <c r="D47">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Kubernetes</v>
+      </c>
+      <c r="C48">
+        <v>313</v>
+      </c>
+      <c r="D48">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Networking</v>
+      </c>
+      <c r="C49">
+        <v>314</v>
+      </c>
+      <c r="D49">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Google GCP</v>
+      </c>
+      <c r="C50">
+        <v>315</v>
+      </c>
+      <c r="D50">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Azure</v>
+      </c>
+      <c r="C51">
+        <v>316</v>
+      </c>
+      <c r="D51">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Talks</v>
+      </c>
+      <c r="C52">
+        <v>401</v>
+      </c>
+      <c r="D52">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B53" t="str">
+        <v>LLM</v>
+      </c>
+      <c r="C53">
+        <v>402</v>
+      </c>
+      <c r="D53">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Prompt Engineering</v>
+      </c>
+      <c r="C54">
+        <v>403</v>
+      </c>
+      <c r="D54">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Vector DB</v>
+      </c>
+      <c r="C55">
+        <v>404</v>
+      </c>
+      <c r="D55">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B56" t="str">
+        <v>RAG</v>
+      </c>
+      <c r="C56">
+        <v>405</v>
+      </c>
+      <c r="D56">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B57" t="str">
+        <v>AI Agent</v>
+      </c>
+      <c r="C57">
+        <v>406</v>
+      </c>
+      <c r="D57">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B58" t="str">
+        <v>MCP</v>
+      </c>
+      <c r="C58">
+        <v>407</v>
+      </c>
+      <c r="D58">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Agentic AI</v>
+      </c>
+      <c r="C59">
+        <v>408</v>
+      </c>
+      <c r="D59">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B60" t="str">
+        <v>GenAI</v>
+      </c>
+      <c r="C60">
+        <v>409</v>
+      </c>
+      <c r="D60">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Voice Bot</v>
+      </c>
+      <c r="C61">
+        <v>410</v>
+      </c>
+      <c r="D61">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B62" t="str">
+        <v>AI Coding</v>
+      </c>
+      <c r="C62">
+        <v>411</v>
+      </c>
+      <c r="D62">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Concepts</v>
+      </c>
+      <c r="C63">
+        <v>412</v>
+      </c>
+      <c r="D63">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B64" t="str">
+        <v>AI Tools</v>
+      </c>
+      <c r="C64">
+        <v>413</v>
+      </c>
+      <c r="D64">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>AI/LLM</v>
+      </c>
+      <c r="B65" t="str">
+        <v>n8n</v>
+      </c>
+      <c r="C65">
+        <v>414</v>
+      </c>
+      <c r="D65">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B66" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="C66">
+        <v>501</v>
+      </c>
+      <c r="D66">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Load Balancer</v>
+      </c>
+      <c r="C67">
+        <v>503</v>
+      </c>
+      <c r="D67">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B68" t="str">
+        <v>DNS</v>
+      </c>
+      <c r="C68">
+        <v>504</v>
+      </c>
+      <c r="D68">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Rate Limiting</v>
+      </c>
+      <c r="C69">
+        <v>505</v>
+      </c>
+      <c r="D69">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Batch Processing</v>
+      </c>
+      <c r="C70">
+        <v>506</v>
+      </c>
+      <c r="D70">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>System Design</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Talks</v>
+      </c>
+      <c r="C71">
+        <v>509</v>
+      </c>
+      <c r="D71">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B72" t="str">
+        <v>IoT</v>
+      </c>
+      <c r="C72">
+        <v>601</v>
+      </c>
+      <c r="D72">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Raspberry Pi</v>
+      </c>
+      <c r="C73">
+        <v>602</v>
+      </c>
+      <c r="D73">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B74" t="str">
+        <v>React Native</v>
+      </c>
+      <c r="C74">
+        <v>603</v>
+      </c>
+      <c r="D74">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Electron JS</v>
+      </c>
+      <c r="C75">
+        <v>604</v>
+      </c>
+      <c r="D75">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B76" t="str">
+        <v>C#</v>
+      </c>
+      <c r="C76">
+        <v>605</v>
+      </c>
+      <c r="D76">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B77" t="str">
+        <v>DotNet</v>
+      </c>
+      <c r="C77">
+        <v>606</v>
+      </c>
+      <c r="D77">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Angular</v>
+      </c>
+      <c r="C78">
+        <v>607</v>
+      </c>
+      <c r="D78">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Java</v>
+      </c>
+      <c r="C79">
+        <v>608</v>
+      </c>
+      <c r="D79">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Python</v>
+      </c>
+      <c r="C80">
+        <v>609</v>
+      </c>
+      <c r="D80">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B81" t="str">
+        <v>VueJS</v>
+      </c>
+      <c r="C81">
+        <v>610</v>
+      </c>
+      <c r="D81">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Other Programming</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Mobile Development</v>
+      </c>
+      <c r="C82">
+        <v>611</v>
+      </c>
+      <c r="D82">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Sprituality</v>
+      </c>
+      <c r="C83">
+        <v>701</v>
+      </c>
+      <c r="D83">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Body</v>
+      </c>
+      <c r="C84">
+        <v>702</v>
+      </c>
+      <c r="D84">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Mind</v>
+      </c>
+      <c r="C85">
+        <v>703</v>
+      </c>
+      <c r="D85">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Look</v>
+      </c>
+      <c r="C86">
+        <v>704</v>
+      </c>
+      <c r="D86">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Personality</v>
+      </c>
+      <c r="C87">
+        <v>705</v>
+      </c>
+      <c r="D87">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Learning</v>
+      </c>
+      <c r="C88">
+        <v>706</v>
+      </c>
+      <c r="D88">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Financial</v>
+      </c>
+      <c r="C89">
+        <v>707</v>
+      </c>
+      <c r="D89">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Business</v>
+      </c>
+      <c r="C90">
+        <v>708</v>
+      </c>
+      <c r="D90">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Life Planning</v>
+      </c>
+      <c r="C91">
+        <v>709</v>
+      </c>
+      <c r="D91">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Hobbies</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Chess</v>
+      </c>
+      <c r="C92">
+        <v>801</v>
+      </c>
+      <c r="D92">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B93" t="str">
+        <v>NotebookLM</v>
+      </c>
+      <c r="C93">
+        <v>901</v>
+      </c>
+      <c r="D93">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Notion</v>
+      </c>
+      <c r="C94">
+        <v>902</v>
+      </c>
+      <c r="D94">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Other</v>
+      </c>
+      <c r="C95">
+        <v>903</v>
+      </c>
+      <c r="D95">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B96" t="str">
+        <v>IT</v>
+      </c>
+      <c r="C96">
+        <v>904</v>
+      </c>
+      <c r="D96">
+        <v>904</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/03_Learning_Management/00_Excel_Export/priorities.xlsx
+++ b/03_Learning_Management/00_Excel_Export/priorities.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,16 +415,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>General</v>
+        <v>Other Programming</v>
       </c>
       <c r="B2" t="str">
-        <v>Communication Skill</v>
+        <v>Go Lang</v>
       </c>
       <c r="C2">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>General</v>
       </c>
       <c r="B3" t="str">
-        <v>English</v>
+        <v>Communication Skill</v>
       </c>
       <c r="C3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>General</v>
       </c>
       <c r="B4" t="str">
-        <v>Aptitude</v>
+        <v>English</v>
       </c>
       <c r="C4">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -460,13 +460,13 @@
         <v>General</v>
       </c>
       <c r="B5" t="str">
-        <v>General Learning</v>
+        <v>Aptitude</v>
       </c>
       <c r="C5">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D5">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -474,27 +474,27 @@
         <v>General</v>
       </c>
       <c r="B6" t="str">
-        <v>Maths</v>
+        <v>General Learning</v>
       </c>
       <c r="C6">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D6">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>WebDev</v>
+        <v>General</v>
       </c>
       <c r="B7" t="str">
-        <v>Talks</v>
+        <v>Maths</v>
       </c>
       <c r="C7">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="D7">
-        <v>201</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -502,13 +502,13 @@
         <v>WebDev</v>
       </c>
       <c r="B8" t="str">
-        <v>HTML</v>
+        <v>Talks</v>
       </c>
       <c r="C8">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D8">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -516,13 +516,13 @@
         <v>WebDev</v>
       </c>
       <c r="B9" t="str">
-        <v>CSS</v>
+        <v>HTML</v>
       </c>
       <c r="C9">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D9">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -530,13 +530,13 @@
         <v>WebDev</v>
       </c>
       <c r="B10" t="str">
-        <v>JavaScript</v>
+        <v>CSS</v>
       </c>
       <c r="C10">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D10">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -544,13 +544,13 @@
         <v>WebDev</v>
       </c>
       <c r="B11" t="str">
-        <v>FrontEnd</v>
+        <v>JavaScript</v>
       </c>
       <c r="C11">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D11">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -558,13 +558,13 @@
         <v>WebDev</v>
       </c>
       <c r="B12" t="str">
-        <v>Git</v>
+        <v>FrontEnd</v>
       </c>
       <c r="C12">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D12">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -572,13 +572,13 @@
         <v>WebDev</v>
       </c>
       <c r="B13" t="str">
-        <v>NodeJS</v>
+        <v>Git</v>
       </c>
       <c r="C13">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D13">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14">
@@ -586,13 +586,13 @@
         <v>WebDev</v>
       </c>
       <c r="B14" t="str">
-        <v>ExpressJS</v>
+        <v>NodeJS</v>
       </c>
       <c r="C14">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D14">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -600,13 +600,13 @@
         <v>WebDev</v>
       </c>
       <c r="B15" t="str">
-        <v>ReactJS</v>
+        <v>ExpressJS</v>
       </c>
       <c r="C15">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D15">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
@@ -614,13 +614,13 @@
         <v>WebDev</v>
       </c>
       <c r="B16" t="str">
-        <v>Redux</v>
+        <v>ReactJS</v>
       </c>
       <c r="C16">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D16">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17">
@@ -628,13 +628,13 @@
         <v>WebDev</v>
       </c>
       <c r="B17" t="str">
-        <v>MongoDB</v>
+        <v>Redux</v>
       </c>
       <c r="C17">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D17">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
@@ -642,13 +642,13 @@
         <v>WebDev</v>
       </c>
       <c r="B18" t="str">
-        <v>SQL</v>
+        <v>MongoDB</v>
       </c>
       <c r="C18">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D18">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
@@ -656,13 +656,13 @@
         <v>WebDev</v>
       </c>
       <c r="B19" t="str">
-        <v>MySQL</v>
+        <v>SQL</v>
       </c>
       <c r="C19">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D19">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
@@ -670,13 +670,13 @@
         <v>WebDev</v>
       </c>
       <c r="B20" t="str">
-        <v>Backend</v>
+        <v>MySQL</v>
       </c>
       <c r="C20">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D20">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
@@ -684,13 +684,13 @@
         <v>WebDev</v>
       </c>
       <c r="B21" t="str">
-        <v>BootStrap</v>
+        <v>Backend</v>
       </c>
       <c r="C21">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D21">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22">
@@ -698,13 +698,13 @@
         <v>WebDev</v>
       </c>
       <c r="B22" t="str">
-        <v>Tailwind</v>
+        <v>BootStrap</v>
       </c>
       <c r="C22">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D22">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23">
@@ -712,13 +712,13 @@
         <v>WebDev</v>
       </c>
       <c r="B23" t="str">
-        <v>MERN</v>
+        <v>Tailwind</v>
       </c>
       <c r="C23">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24">
@@ -726,13 +726,13 @@
         <v>WebDev</v>
       </c>
       <c r="B24" t="str">
-        <v>TypeScript</v>
+        <v>MERN</v>
       </c>
       <c r="C24">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D24">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25">
@@ -740,13 +740,13 @@
         <v>WebDev</v>
       </c>
       <c r="B25" t="str">
-        <v>PostgreSQL</v>
+        <v>TypeScript</v>
       </c>
       <c r="C25">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D25">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26">
@@ -754,13 +754,13 @@
         <v>WebDev</v>
       </c>
       <c r="B26" t="str">
-        <v>NextJS</v>
+        <v>PostgreSQL</v>
       </c>
       <c r="C26">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D26">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27">
@@ -768,13 +768,13 @@
         <v>WebDev</v>
       </c>
       <c r="B27" t="str">
-        <v>DSA</v>
+        <v>NextJS</v>
       </c>
       <c r="C27">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D27">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
@@ -782,13 +782,13 @@
         <v>WebDev</v>
       </c>
       <c r="B28" t="str">
-        <v>Redis</v>
+        <v>DSA</v>
       </c>
       <c r="C28">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D28">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29">
@@ -796,13 +796,13 @@
         <v>WebDev</v>
       </c>
       <c r="B29" t="str">
-        <v>Supabase</v>
+        <v>Redis</v>
       </c>
       <c r="C29">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D29">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30">
@@ -810,13 +810,13 @@
         <v>WebDev</v>
       </c>
       <c r="B30" t="str">
-        <v>NestJS</v>
+        <v>Supabase</v>
       </c>
       <c r="C30">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D30">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31">
@@ -824,13 +824,13 @@
         <v>WebDev</v>
       </c>
       <c r="B31" t="str">
-        <v>Web Dev</v>
+        <v>NestJS</v>
       </c>
       <c r="C31">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D31">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32">
@@ -838,13 +838,13 @@
         <v>WebDev</v>
       </c>
       <c r="B32" t="str">
-        <v>GraphQL</v>
+        <v>Web Dev</v>
       </c>
       <c r="C32">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D32">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33">
@@ -852,13 +852,13 @@
         <v>WebDev</v>
       </c>
       <c r="B33" t="str">
-        <v>gRPC</v>
+        <v>GraphQL</v>
       </c>
       <c r="C33">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D33">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34">
@@ -866,13 +866,13 @@
         <v>WebDev</v>
       </c>
       <c r="B34" t="str">
-        <v>MicroServices</v>
+        <v>gRPC</v>
       </c>
       <c r="C34">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D34">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35">
@@ -880,27 +880,27 @@
         <v>WebDev</v>
       </c>
       <c r="B35" t="str">
-        <v>Concepts</v>
+        <v>MicroServices</v>
       </c>
       <c r="C35">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D35">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Deployment</v>
+        <v>WebDev</v>
       </c>
       <c r="B36" t="str">
-        <v>Talks</v>
+        <v>Concepts</v>
       </c>
       <c r="C36">
-        <v>301</v>
+        <v>229</v>
       </c>
       <c r="D36">
-        <v>301</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37">
@@ -908,13 +908,13 @@
         <v>Deployment</v>
       </c>
       <c r="B37" t="str">
-        <v>Docker</v>
+        <v>Talks</v>
       </c>
       <c r="C37">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D37">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38">
@@ -922,13 +922,13 @@
         <v>Deployment</v>
       </c>
       <c r="B38" t="str">
-        <v>SSH</v>
+        <v>Docker</v>
       </c>
       <c r="C38">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D38">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39">
@@ -936,13 +936,13 @@
         <v>Deployment</v>
       </c>
       <c r="B39" t="str">
-        <v>Jenkins</v>
+        <v>SSH</v>
       </c>
       <c r="C39">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40">
@@ -950,13 +950,13 @@
         <v>Deployment</v>
       </c>
       <c r="B40" t="str">
-        <v>Linux</v>
+        <v>Jenkins</v>
       </c>
       <c r="C40">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41">
@@ -964,13 +964,13 @@
         <v>Deployment</v>
       </c>
       <c r="B41" t="str">
-        <v>Deployment</v>
+        <v>Linux</v>
       </c>
       <c r="C41">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D41">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42">
@@ -978,13 +978,13 @@
         <v>Deployment</v>
       </c>
       <c r="B42" t="str">
-        <v>DevOps</v>
+        <v>Deployment</v>
       </c>
       <c r="C42">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D42">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43">
@@ -992,13 +992,13 @@
         <v>Deployment</v>
       </c>
       <c r="B43" t="str">
-        <v>AWS</v>
+        <v>DevOps</v>
       </c>
       <c r="C43">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D43">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44">
@@ -1006,13 +1006,13 @@
         <v>Deployment</v>
       </c>
       <c r="B44" t="str">
-        <v>ArgoCD</v>
+        <v>AWS</v>
       </c>
       <c r="C44">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D44">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45">
@@ -1020,13 +1020,13 @@
         <v>Deployment</v>
       </c>
       <c r="B45" t="str">
-        <v>CloudFlare</v>
+        <v>ArgoCD</v>
       </c>
       <c r="C45">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D45">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46">
@@ -1034,13 +1034,13 @@
         <v>Deployment</v>
       </c>
       <c r="B46" t="str">
-        <v>Kafka</v>
+        <v>CloudFlare</v>
       </c>
       <c r="C46">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D46">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47">
@@ -1048,13 +1048,13 @@
         <v>Deployment</v>
       </c>
       <c r="B47" t="str">
-        <v>Concepts</v>
+        <v>Kafka</v>
       </c>
       <c r="C47">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D47">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48">
@@ -1062,13 +1062,13 @@
         <v>Deployment</v>
       </c>
       <c r="B48" t="str">
-        <v>Kubernetes</v>
+        <v>Concepts</v>
       </c>
       <c r="C48">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D48">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49">
@@ -1076,13 +1076,13 @@
         <v>Deployment</v>
       </c>
       <c r="B49" t="str">
-        <v>Networking</v>
+        <v>Kubernetes</v>
       </c>
       <c r="C49">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D49">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50">
@@ -1090,13 +1090,13 @@
         <v>Deployment</v>
       </c>
       <c r="B50" t="str">
-        <v>Google GCP</v>
+        <v>Networking</v>
       </c>
       <c r="C50">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D50">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51">
@@ -1104,41 +1104,41 @@
         <v>Deployment</v>
       </c>
       <c r="B51" t="str">
-        <v>Azure</v>
+        <v>Google GCP</v>
       </c>
       <c r="C51">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D51">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>AI/LLM</v>
+        <v>Deployment</v>
       </c>
       <c r="B52" t="str">
-        <v>Talks</v>
+        <v>Azure</v>
       </c>
       <c r="C52">
-        <v>401</v>
+        <v>316</v>
       </c>
       <c r="D52">
-        <v>401</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>AI/LLM</v>
+        <v>Deployment</v>
       </c>
       <c r="B53" t="str">
-        <v>LLM</v>
+        <v>GitHub Actions</v>
       </c>
       <c r="C53">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="D53">
-        <v>402</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54">
@@ -1146,13 +1146,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B54" t="str">
-        <v>Prompt Engineering</v>
+        <v>Talks</v>
       </c>
       <c r="C54">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D54">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="55">
@@ -1160,13 +1160,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B55" t="str">
-        <v>Vector DB</v>
+        <v>LLM</v>
       </c>
       <c r="C55">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D55">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56">
@@ -1174,13 +1174,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B56" t="str">
-        <v>RAG</v>
+        <v>Prompt Engineering</v>
       </c>
       <c r="C56">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D56">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="57">
@@ -1188,13 +1188,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B57" t="str">
-        <v>AI Agent</v>
+        <v>Vector DB</v>
       </c>
       <c r="C57">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D57">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="58">
@@ -1202,13 +1202,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B58" t="str">
-        <v>MCP</v>
+        <v>RAG</v>
       </c>
       <c r="C58">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D58">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="59">
@@ -1216,13 +1216,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B59" t="str">
-        <v>Agentic AI</v>
+        <v>AI Agent</v>
       </c>
       <c r="C59">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D59">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60">
@@ -1230,13 +1230,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B60" t="str">
-        <v>GenAI</v>
+        <v>MCP</v>
       </c>
       <c r="C60">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D60">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="61">
@@ -1244,13 +1244,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B61" t="str">
-        <v>Voice Bot</v>
+        <v>Agentic AI</v>
       </c>
       <c r="C61">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D61">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="62">
@@ -1258,13 +1258,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B62" t="str">
-        <v>AI Coding</v>
+        <v>GenAI</v>
       </c>
       <c r="C62">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D62">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63">
@@ -1272,13 +1272,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B63" t="str">
-        <v>Concepts</v>
+        <v>Voice Bot</v>
       </c>
       <c r="C63">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D63">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64">
@@ -1286,13 +1286,13 @@
         <v>AI/LLM</v>
       </c>
       <c r="B64" t="str">
-        <v>AI Tools</v>
+        <v>AI Coding</v>
       </c>
       <c r="C64">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D64">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65">
@@ -1300,69 +1300,69 @@
         <v>AI/LLM</v>
       </c>
       <c r="B65" t="str">
-        <v>n8n</v>
+        <v>Concepts</v>
       </c>
       <c r="C65">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D65">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System Design</v>
+        <v>AI/LLM</v>
       </c>
       <c r="B66" t="str">
-        <v>System Design</v>
+        <v>AI Tools</v>
       </c>
       <c r="C66">
-        <v>501</v>
+        <v>413</v>
       </c>
       <c r="D66">
-        <v>501</v>
+        <v>413</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System Design</v>
+        <v>AI/LLM</v>
       </c>
       <c r="B67" t="str">
-        <v>Load Balancer</v>
+        <v>n8n</v>
       </c>
       <c r="C67">
-        <v>503</v>
+        <v>414</v>
       </c>
       <c r="D67">
-        <v>503</v>
+        <v>414</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>System Design</v>
+        <v>AI/LLM</v>
       </c>
       <c r="B68" t="str">
-        <v>DNS</v>
+        <v>Hugging Face</v>
       </c>
       <c r="C68">
-        <v>504</v>
+        <v>415</v>
       </c>
       <c r="D68">
-        <v>504</v>
+        <v>415</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>System Design</v>
+        <v>AI/LLM</v>
       </c>
       <c r="B69" t="str">
-        <v>Rate Limiting</v>
+        <v>OpenClaw</v>
       </c>
       <c r="C69">
-        <v>505</v>
+        <v>416</v>
       </c>
       <c r="D69">
-        <v>505</v>
+        <v>416</v>
       </c>
     </row>
     <row r="70">
@@ -1370,13 +1370,13 @@
         <v>System Design</v>
       </c>
       <c r="B70" t="str">
-        <v>Batch Processing</v>
+        <v>System Design</v>
       </c>
       <c r="C70">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D70">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="71">
@@ -1384,83 +1384,83 @@
         <v>System Design</v>
       </c>
       <c r="B71" t="str">
-        <v>Talks</v>
+        <v>Load Balancer</v>
       </c>
       <c r="C71">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D71">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Other Programming</v>
+        <v>System Design</v>
       </c>
       <c r="B72" t="str">
-        <v>IoT</v>
+        <v>DNS</v>
       </c>
       <c r="C72">
-        <v>601</v>
+        <v>504</v>
       </c>
       <c r="D72">
-        <v>601</v>
+        <v>504</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Other Programming</v>
+        <v>System Design</v>
       </c>
       <c r="B73" t="str">
-        <v>Raspberry Pi</v>
+        <v>Rate Limiting</v>
       </c>
       <c r="C73">
-        <v>602</v>
+        <v>505</v>
       </c>
       <c r="D73">
-        <v>602</v>
+        <v>505</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Other Programming</v>
+        <v>System Design</v>
       </c>
       <c r="B74" t="str">
-        <v>React Native</v>
+        <v>Batch Processing</v>
       </c>
       <c r="C74">
-        <v>603</v>
+        <v>506</v>
       </c>
       <c r="D74">
-        <v>603</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Other Programming</v>
+        <v>System Design</v>
       </c>
       <c r="B75" t="str">
-        <v>Electron JS</v>
+        <v>Talks</v>
       </c>
       <c r="C75">
-        <v>604</v>
+        <v>509</v>
       </c>
       <c r="D75">
-        <v>604</v>
+        <v>509</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Other Programming</v>
+        <v>System Design</v>
       </c>
       <c r="B76" t="str">
-        <v>C#</v>
+        <v>Event Driven System</v>
       </c>
       <c r="C76">
-        <v>605</v>
+        <v>510</v>
       </c>
       <c r="D76">
-        <v>605</v>
+        <v>510</v>
       </c>
     </row>
     <row r="77">
@@ -1468,13 +1468,13 @@
         <v>Other Programming</v>
       </c>
       <c r="B77" t="str">
-        <v>DotNet</v>
+        <v>IoT</v>
       </c>
       <c r="C77">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D77">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="78">
@@ -1482,13 +1482,13 @@
         <v>Other Programming</v>
       </c>
       <c r="B78" t="str">
-        <v>Angular</v>
+        <v>Raspberry Pi</v>
       </c>
       <c r="C78">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D78">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="79">
@@ -1496,13 +1496,13 @@
         <v>Other Programming</v>
       </c>
       <c r="B79" t="str">
-        <v>Java</v>
+        <v>React Native</v>
       </c>
       <c r="C79">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D79">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="80">
@@ -1510,13 +1510,13 @@
         <v>Other Programming</v>
       </c>
       <c r="B80" t="str">
-        <v>Python</v>
+        <v>Electron JS</v>
       </c>
       <c r="C80">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D80">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81">
@@ -1524,13 +1524,13 @@
         <v>Other Programming</v>
       </c>
       <c r="B81" t="str">
-        <v>VueJS</v>
+        <v>C#</v>
       </c>
       <c r="C81">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D81">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="82">
@@ -1538,83 +1538,83 @@
         <v>Other Programming</v>
       </c>
       <c r="B82" t="str">
-        <v>Mobile Development</v>
+        <v>DotNet</v>
       </c>
       <c r="C82">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D82">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Personal</v>
+        <v>Other Programming</v>
       </c>
       <c r="B83" t="str">
-        <v>Sprituality</v>
+        <v>Angular</v>
       </c>
       <c r="C83">
-        <v>701</v>
+        <v>607</v>
       </c>
       <c r="D83">
-        <v>701</v>
+        <v>607</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Personal</v>
+        <v>Other Programming</v>
       </c>
       <c r="B84" t="str">
-        <v>Body</v>
+        <v>Java</v>
       </c>
       <c r="C84">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="D84">
-        <v>702</v>
+        <v>608</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Personal</v>
+        <v>Other Programming</v>
       </c>
       <c r="B85" t="str">
-        <v>Mind</v>
+        <v>Python</v>
       </c>
       <c r="C85">
-        <v>703</v>
+        <v>609</v>
       </c>
       <c r="D85">
-        <v>703</v>
+        <v>609</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Personal</v>
+        <v>Other Programming</v>
       </c>
       <c r="B86" t="str">
-        <v>Look</v>
+        <v>VueJS</v>
       </c>
       <c r="C86">
-        <v>704</v>
+        <v>610</v>
       </c>
       <c r="D86">
-        <v>704</v>
+        <v>610</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Personal</v>
+        <v>Other Programming</v>
       </c>
       <c r="B87" t="str">
-        <v>Personality</v>
+        <v>Mobile Development</v>
       </c>
       <c r="C87">
-        <v>705</v>
+        <v>611</v>
       </c>
       <c r="D87">
-        <v>705</v>
+        <v>611</v>
       </c>
     </row>
     <row r="88">
@@ -1622,13 +1622,13 @@
         <v>Personal</v>
       </c>
       <c r="B88" t="str">
-        <v>Learning</v>
+        <v>Sprituality</v>
       </c>
       <c r="C88">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D88">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
     <row r="89">
@@ -1636,13 +1636,13 @@
         <v>Personal</v>
       </c>
       <c r="B89" t="str">
-        <v>Financial</v>
+        <v>Body</v>
       </c>
       <c r="C89">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="D89">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="90">
@@ -1650,13 +1650,13 @@
         <v>Personal</v>
       </c>
       <c r="B90" t="str">
-        <v>Business</v>
+        <v>Mind</v>
       </c>
       <c r="C90">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="D90">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="91">
@@ -1664,88 +1664,186 @@
         <v>Personal</v>
       </c>
       <c r="B91" t="str">
-        <v>Life Planning</v>
+        <v>Look</v>
       </c>
       <c r="C91">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D91">
-        <v>709</v>
+        <v>704</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Hobbies</v>
+        <v>Personal</v>
       </c>
       <c r="B92" t="str">
-        <v>Chess</v>
+        <v>Personality</v>
       </c>
       <c r="C92">
-        <v>801</v>
+        <v>705</v>
       </c>
       <c r="D92">
-        <v>801</v>
+        <v>705</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Other</v>
+        <v>Personal</v>
       </c>
       <c r="B93" t="str">
-        <v>NotebookLM</v>
+        <v>Learning</v>
       </c>
       <c r="C93">
-        <v>901</v>
+        <v>706</v>
       </c>
       <c r="D93">
-        <v>901</v>
+        <v>706</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Other</v>
+        <v>Personal</v>
       </c>
       <c r="B94" t="str">
-        <v>Notion</v>
+        <v>Financial</v>
       </c>
       <c r="C94">
-        <v>902</v>
+        <v>707</v>
       </c>
       <c r="D94">
-        <v>902</v>
+        <v>707</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Other</v>
+        <v>Personal</v>
       </c>
       <c r="B95" t="str">
-        <v>Other</v>
+        <v>Business</v>
       </c>
       <c r="C95">
-        <v>903</v>
+        <v>708</v>
       </c>
       <c r="D95">
-        <v>903</v>
+        <v>708</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Life Planning</v>
+      </c>
+      <c r="C96">
+        <v>709</v>
+      </c>
+      <c r="D96">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Job</v>
+      </c>
+      <c r="C97">
+        <v>710</v>
+      </c>
+      <c r="D97">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Hobbies</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Chess</v>
+      </c>
+      <c r="C98">
+        <v>801</v>
+      </c>
+      <c r="D98">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
         <v>Other</v>
       </c>
-      <c r="B96" t="str">
+      <c r="B99" t="str">
+        <v>NotebookLM</v>
+      </c>
+      <c r="C99">
+        <v>901</v>
+      </c>
+      <c r="D99">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Notion</v>
+      </c>
+      <c r="C100">
+        <v>902</v>
+      </c>
+      <c r="D100">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Other</v>
+      </c>
+      <c r="C101">
+        <v>903</v>
+      </c>
+      <c r="D101">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B102" t="str">
         <v>IT</v>
       </c>
-      <c r="C96">
+      <c r="C102">
         <v>904</v>
       </c>
-      <c r="D96">
+      <c r="D102">
         <v>904</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Other</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Gaming</v>
+      </c>
+      <c r="C103">
+        <v>905</v>
+      </c>
+      <c r="D103">
+        <v>905</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D103"/>
   </ignoredErrors>
 </worksheet>
 </file>